--- a/registration_forms/049_training_program_calendar--registration_forms.xlsx
+++ b/registration_forms/049_training_program_calendar--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>training_program_calendar</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>training_program_calendar</t>
+          <t>What is the purpose of this training?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,58 +543,58 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>training_sessions</t>
+          <t>page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>training_sessions</t>
+          <t>Which of the following sessions did the participant attend?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>participant_information</t>
+          <t>page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>participant_information</t>
+          <t>What is the participant's name?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>session_details</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>session_details</t>
+          <t>Do you have any questions about the training?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,46 +607,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>What are the notes from the session?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What is the participant's availability for follow-up?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,58 +658,58 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>How many tools do you have used during the training?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>What are the tools used?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Do you have any feedback about the tools?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,46 +722,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>What is your overall satisfaction with the training?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>What is your rating for the training?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,202 +773,64 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Would you recommend this training?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>page_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Do you have any comments about this training?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>page_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Is this the end of the form?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -983,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1011,510 +873,255 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>training_sessions_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>session_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Session 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>training_sessions_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>session_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Session 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>participant_information_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>session_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Session 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>participant_information_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unavailable</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tool_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tool 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tool_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tool 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tool_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tool 3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
